--- a/objects_audit.xlsx
+++ b/objects_audit.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All_Objects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Migration_Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Registry_Gaps" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +58,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -101,6 +117,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -218,6 +243,20 @@
     <tableColumn id="7" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistryGaps" displayName="RegistryGaps" ref="A1:E22" headerRowCount="1">
+  <autoFilter ref="A1:E22"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Kind"/>
+    <tableColumn id="2" name="Table / Item"/>
+    <tableColumn id="3" name="Label / Note"/>
+    <tableColumn id="4" name="Evidence (file:line)"/>
+    <tableColumn id="5" name="Recommended Action"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showRowStripes="0"/>
 </table>
 </file>
 
@@ -510,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -658,6 +697,101 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Primary migration scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REGISTRY GAPS (from AST scan + .sql review)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bug — likely typo</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Django-modeled, not in registry</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total registry gaps</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>See Registry_Gaps sheet</t>
         </is>
       </c>
     </row>
@@ -14299,4 +14433,622 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="73" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Table / Item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Label / Note</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence (file:line)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>homepage_assignment</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Homepage Assignment</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>api/ORM/setup/newprofile.py:88,93</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); will be migrated to Django ORM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>organizations</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Organizations</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>adminuser/services/organizations.py:28,53; api/models.py:Organization</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); already has Django model</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>otp_verification_sessions</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>OTP Verification Sessions</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>public/auth/otp_verification.py:156,198</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); auth/OTP flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>page_builder</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Page Builder</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>api/ORM/setup/update_page_builder.py:28</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); distinct from registered 'page_builder_assignment'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>page_component</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Page Component</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>api/ORM/setup/update_page_builder.py:66,78</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); page-builder child table</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>tenant_provisioning_errors</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Provisioning Errors</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>public/utils/error_log.py:20</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); tenant onboarding error log</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>user_group_profiles</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>User Group Profiles</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>utils/usergroup_utils.py:305</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); junction table for user_group &lt;-&gt; profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>user_group_public_groups</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>User Group Public Groups</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>utils/usergroup_utils.py:317; api/workflows/workflow_executor.py:552</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); junction for nested user groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>whatsapp_message</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>WhatsApp Message</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>api/BL/whatsapp/utils.py:18,67</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); chat-message store</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_component</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard Component</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Add registry row; child of dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_folders</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard Folders</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Plural form referenced; registry has 'dashboard_folder' singular - pick one and reconcile</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>report_folder</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Report Folder</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=FALSE); related to 'reports' (already registered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>dashboard_folder vs dashboard_folders</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Folder</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>registry: dashboard_folder (singular); code: dashboard_folders (plural)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Standardize on one form across registry, code, and mockdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>reports vs report vs report_folder</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>registry: 'reports'; code uses 'report' and 'report_folder' too</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Standardize and register all related tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Bug — likely typo</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>hsitory</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Probably means 'history'</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>registry row in objects.sql</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Rename to 'history' before migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Bug — likely typo</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>organization (singular)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Probably means 'organizations'</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>api/pdfgen/views.py:74</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Fix the SQL string to use 'organizations'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>customers (setup) vs customer (business)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>invoice_items (setup) vs invoice_item (business)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Item</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>invoices (setup) vs invoice (business)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>products (setup) vs product (business)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Django-modeled, not in registry</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>facebookleadwebhooks</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Facebook Lead Webhooks</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>facebook/models.py (currently commented out)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Add registry row OR delete the Django model — currently dead code</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/objects_audit.xlsx
+++ b/objects_audit.xlsx
@@ -11,6 +11,7 @@
     <sheet name="All_Objects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Migration_Plan" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Registry_Gaps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DDL_Cross_Check" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +76,11 @@
         <fgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAEAEA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -126,6 +132,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -247,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistryGaps" displayName="RegistryGaps" ref="A1:E22" headerRowCount="1">
-  <autoFilter ref="A1:E22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistryGaps" displayName="RegistryGaps" ref="A1:E41" headerRowCount="1">
+  <autoFilter ref="A1:E41"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Kind"/>
     <tableColumn id="2" name="Table / Item"/>
@@ -257,6 +266,24 @@
     <tableColumn id="5" name="Recommended Action"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DDLCrossCheck" displayName="DDLCrossCheck" ref="A1:I152" headerRowCount="1">
+  <autoFilter ref="A1:I152"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Table Name"/>
+    <tableColumn id="2" name="In Registry"/>
+    <tableColumn id="3" name="Registry Type"/>
+    <tableColumn id="4" name="default_tables.sql"/>
+    <tableColumn id="5" name="tables.sql"/>
+    <tableColumn id="6" name="Inline organisation.py"/>
+    <tableColumn id="7" name="App models.py"/>
+    <tableColumn id="8" name="Phase 2 Wave 2 model"/>
+    <tableColumn id="9" name="Verdict"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -721,7 +748,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -732,7 +759,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -743,7 +770,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -787,7 +814,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -14441,13 +14468,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="73" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -14486,22 +14513,22 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>homepage_assignment</t>
+          <t>callactivity</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Homepage Assignment</t>
+          <t>Call Activity</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>api/ORM/setup/newprofile.py:88,93</t>
+          <t>default_tables.sql:933</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); will be migrated to Django ORM</t>
+          <t>Add registry row (setup=TRUE); telephony call-activity log</t>
         </is>
       </c>
     </row>
@@ -14513,22 +14540,22 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>organizations</t>
+          <t>dashboard_assignment</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Organizations</t>
+          <t>Dashboard Assignment</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>adminuser/services/organizations.py:28,53; api/models.py:Organization</t>
+          <t>default_tables.sql (dashboard module)</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); already has Django model</t>
+          <t>Add registry row (setup=TRUE); dashboard share assignment</t>
         </is>
       </c>
     </row>
@@ -14540,22 +14567,22 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>otp_verification_sessions</t>
+          <t>dashboard_folder_sharing</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>OTP Verification Sessions</t>
+          <t>Dashboard Folder Sharing</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>public/auth/otp_verification.py:156,198</t>
+          <t>default_tables.sql:739</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); auth/OTP flow</t>
+          <t>Add registry row (setup=TRUE)</t>
         </is>
       </c>
     </row>
@@ -14567,22 +14594,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>page_builder</t>
+          <t>email_provider_setup</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>Email Provider Setup</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>api/ORM/setup/update_page_builder.py:28</t>
+          <t>default_tables.sql:785</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); distinct from registered 'page_builder_assignment'</t>
+          <t>Add registry row (setup=TRUE); OAuth-token storage (encrypted since Phase 0.8)</t>
         </is>
       </c>
     </row>
@@ -14594,22 +14621,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>page_component</t>
+          <t>field_mapping</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Page Component</t>
+          <t>Field Mapping</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>api/ORM/setup/update_page_builder.py:66,78</t>
+          <t>default_tables.sql:146</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); page-builder child table</t>
+          <t>Add registry row (setup=TRUE)</t>
         </is>
       </c>
     </row>
@@ -14621,22 +14648,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>tenant_provisioning_errors</t>
+          <t>homepage_assignment</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Tenant Provisioning Errors</t>
+          <t>Homepage Assignment</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>public/utils/error_log.py:20</t>
+          <t>api/ORM/setup/newprofile.py:88,93</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); tenant onboarding error log</t>
+          <t>Add registry row (setup=TRUE); will be migrated to Django ORM</t>
         </is>
       </c>
     </row>
@@ -14648,22 +14675,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>user_group_profiles</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>User Group Profiles</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>utils/usergroup_utils.py:305</t>
+          <t>default_tables.sql:905</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); junction table for user_group &lt;-&gt; profile</t>
+          <t>Add registry row (setup=TRUE); registry currently has BL route name 'notification' but no entry for the actual table</t>
         </is>
       </c>
     </row>
@@ -14675,22 +14702,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>user_group_public_groups</t>
+          <t>org_company</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>User Group Public Groups</t>
+          <t>Organization Company</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>utils/usergroup_utils.py:317; api/workflows/workflow_executor.py:552</t>
+          <t>default_tables.sql (legacy column-mapping table)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Add registry row (setup=TRUE); junction for nested user groups</t>
+          <t>Add registry row (setup=TRUE); investigate whether still used</t>
         </is>
       </c>
     </row>
@@ -14702,346 +14729,5419 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>organizations</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Organizations</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>adminuser/services/organizations.py:28,53; api/models.py:Organization</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); already has Django model</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>otp_verification_sessions</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>OTP Verification Sessions</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>public/auth/otp_verification.py:156,198</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); auth/OTP flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>page_builder</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Page Builder</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>api/ORM/setup/update_page_builder.py:28</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); distinct from registered 'page_builder_assignment'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>page_component</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Page Component</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>api/ORM/setup/update_page_builder.py:66,78</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); page-builder child table</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>report_folder_sharing</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Report Folder Sharing</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>default_tables.sql:847</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>shared_records</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Shared Records (per-record sharing)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>default_tables.sql:873</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); DISTINCT from 'sharing_records' — sharing_records is per-object, shared_records is per-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>telephony_user</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Telephony User</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>default_tables.sql:923</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); referenced in api/telephony/views.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>tenant_provisioning_errors</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Provisioning Errors</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>public/utils/error_log.py:20</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); tenant onboarding error log</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>user_gmail_tokens</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>User Gmail Tokens</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>default_tables.sql:705</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); legacy — superseded by email_provider_setup but still created</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>user_group_profiles</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>User Group Profiles</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>utils/usergroup_utils.py:305</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); junction table for user_group &lt;-&gt; profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>user_group_public_groups</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>User Group Public Groups</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>utils/usergroup_utils.py:317; api/workflows/workflow_executor.py:552</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); junction for nested user groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>user_outlook_tokens</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>User Outlook Tokens</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>default_tables.sql:720</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=TRUE); legacy — superseded by email_provider_setup but still created</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Missing setup table</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>whatsapp_message</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>WhatsApp Message</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>api/BL/whatsapp/utils.py:18,67</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Add registry row (setup=TRUE); chat-message store</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>tables.sql defines `CREATE TABLE activity` but it's not in the object registry as a business object</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Register as business object (setup=FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_component</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard Component</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Add registry row; child of dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_folders</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard Folders</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Plural form referenced; registry has 'dashboard_folder' singular - pick one and reconcile</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Email (record)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>tables.sql defines `CREATE TABLE email` for sent-email logging; not in the registry</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Register as business object (setup=FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Missing business object</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>report_folder</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Report Folder</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>sqlfiles/mockdata/reports.sql</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Add registry row (setup=FALSE); related to 'reports' (already registered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>dashboard_folder vs dashboard_folders</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Folder</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>registry: dashboard_folder (singular); code: dashboard_folders (plural)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Standardize on one form across registry, code, and mockdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>report (default_tables.sql) vs reports (registry)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>default_tables.sql:320 has `CREATE TABLE report`; registry has 'reports' as the setup name</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Pick one: either rename DDL to reports or update the registry to use 'report'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>reports vs report vs report_folder</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>registry: 'reports'; code uses 'report' and 'report_folder' too</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Standardize and register all related tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>shared_records vs sharing_records</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Two genuinely different tables, names too similar</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>default_tables.sql defines BOTH; sharing_records is per-object, shared_records is per-record</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Rename one to disambiguate (suggest: per_record_shares) and update all references</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Bug — likely typo</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>hsitory</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Probably means 'history'</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>registry row in objects.sql</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Rename to 'history' before migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Bug — likely typo</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>organization (singular)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Probably means 'organizations'</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>api/pdfgen/views.py:74</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Fix the SQL string to use 'organizations'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>customers (setup) vs customer (business)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>invoice_items (setup) vs invoice_item (business)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Item</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>invoices (setup) vs invoice (business)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Legacy duplicate</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>products (setup) vs product (business)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>objects.sql registers both</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Investigate which is actually used; merge or delete the unused one</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Django-modeled, not in registry</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>facebookleadwebhooks</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Facebook Lead Webhooks</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>facebook/models.py (currently commented out)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Add registry row OR delete the Django model — currently dead code</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Vestigial registry entry</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>apex_class, approval_processes, auth_group, columns_metadata, component, connected_app, custom_metadata, custom_setting, duplicate_rule, file, flows, group_assignment_tracker, import_wizard, lead_capture, lightning_pages, matching_rule, named_credential, node, package, permission_sets, process_builders, regions, remote_site_setting, sales, setup, sf_integration_lead, sharing_rules, tables_metadata, tabs, theme, users_user_permissions, workflow_rules</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Aspirational Salesforce-clone features</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Registered as setup=TRUE but no DDL in default_tables.sql, organisation.py, or app models; no SQL queries reference them</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Bulk-investigate; delete vestigial rows after confirming none are queried at runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Vestigial registry entry</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>owd</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Org-Wide Defaults table</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Registered as setup=TRUE but no DDL anywhere; no FROM owd queries. Phase 2 default-deny work uses sharing_records exclusively.</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Either build out OR delete the registry row + drop the Wave 2 OrganizationWideDefault model</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Vestigial registry entry</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Aspirational Salesforce-style role hierarchy</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Registered as setup=TRUE but no CREATE TABLE in tables.sql / default_tables.sql / organisation.py / app models; no FROM roles queries in the codebase</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Either build out the role-hierarchy feature OR delete the registry row + drop the Wave 2 Role model</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I152"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>In Registry</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Registry Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>default_tables.sql</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tables.sql</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Inline organisation.py</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>App models.py</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 2 Wave 2 model</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>an_object_for_testing</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>apex_class</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>app_permissions</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>approval_processes</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>audit_trail_track</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>audit_trails</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Missing business object</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>dashboard_component</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Dashboard Component</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>sqlfiles/mockdata/reports.sql</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Add registry row; child of dashboard</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>auth_group</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Missing business object</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>dashboard_folders</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Dashboard Folders</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>sqlfiles/mockdata/reports.sql</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Plural form referenced; registry has 'dashboard_folder' singular - pick one and reconcile</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>auth_group_permissions</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Missing business object</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>report_folder</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Report Folder</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>sqlfiles/mockdata/reports.sql</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Add registry row (setup=FALSE); related to 'reports' (already registered)</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>auth_permission</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Naming inconsistency</t>
+          <t>business</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>dashboard_folder vs dashboard_folders</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Folder</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>registry: dashboard_folder (singular); code: dashboard_folders (plural)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Standardize on one form across registry, code, and mockdata</t>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Naming inconsistency</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>reports vs report vs report_folder</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>registry: 'reports'; code uses 'report' and 'report_folder' too</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Standardize and register all related tables</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>calendar</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Bug — likely typo</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>hsitory</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Probably means 'history'</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>registry row in objects.sql</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Rename to 'history' before migration</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Bug — likely typo</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>organization (singular)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Probably means 'organizations'</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>api/pdfgen/views.py:74</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Fix the SQL string to use 'organizations'</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>call_logs</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Legacy duplicate</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>customers (setup) vs customer (business)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>objects.sql registers both</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Investigate which is actually used; merge or delete the unused one</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>callactivity</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Legacy duplicate</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>invoice_items (setup) vs invoice_item (business)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Invoice Item</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>objects.sql registers both</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Investigate which is actually used; merge or delete the unused one</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>campaign</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Legacy duplicate</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>invoices (setup) vs invoice (business)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>objects.sql registers both</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Investigate which is actually used; merge or delete the unused one</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>campaign_member</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Legacy duplicate</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>products (setup) vs product (business)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>objects.sql registers both</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Investigate which is actually used; merge or delete the unused one</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Django-modeled, not in registry</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>columns_metadata</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>connected_app</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>custom_metadata</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>custom_setting</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_assignment</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_component</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>dashboard_folder</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_folder_sharing</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>dashboard_folders</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>django_admin_log</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_clockedschedule</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_crontabschedule</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_intervalschedule</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_periodictask</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_periodictasks</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>django_celery_beat_solarschedule</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>django_content_type</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="inlineStr"/>
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>django_migrations</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="9" t="inlineStr"/>
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>django_session</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr"/>
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="9" t="inlineStr"/>
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>duplicate_rule</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>email_provider_setup</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>email_templates</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>facebook_lead</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
           <t>facebookleadwebhooks</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Facebook Lead Webhooks</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>facebook/models.py (currently commented out)</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Add registry row OR delete the Django model — currently dead code</t>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>field_history_log</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>field_mapping</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>field_permissions</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>field_tracking_config</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>fields</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>flows</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>group_assignment_tracker</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>homepage_assignment</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>hsitory</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>import_wizard</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>incentive_slab</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>invoice_item</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>invoice_items</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>issue</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>landing_numbers</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>layout_assignment</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>lead_capture</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>lightning_pages</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>listviews</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>location_track</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>matching_rule</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>named_credential</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>node</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>object_permissions</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>opportunity</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>opportunity_lineitem</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>org_company</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>organizations</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="7" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>owd</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>page_builder</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>page_builder_assignment</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>page_component</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>page_layouts</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>path_builder</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>permission_sets</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>process_builders</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="3" t="inlineStr"/>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>product_category</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>products</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr"/>
+      <c r="F103" s="3" t="inlineStr"/>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>quote_line_item</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>remote_site_setting</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>report_folder</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr"/>
+      <c r="F110" s="7" t="inlineStr"/>
+      <c r="G110" s="7" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>report_folder_sharing</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr"/>
+      <c r="F111" s="7" t="inlineStr"/>
+      <c r="G111" s="7" t="inlineStr"/>
+      <c r="H111" s="7" t="inlineStr"/>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>reports</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>salesforce_metadata</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>salesforce_settings</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>salesforce_sync</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>search_layouts</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>session_log</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr"/>
+      <c r="F120" s="3" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>sf_integration_lead</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr"/>
+      <c r="E121" s="3" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>shared_records</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr"/>
+      <c r="F122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr"/>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>sharing_records</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>sharing_rules</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr"/>
+      <c r="F124" s="3" t="inlineStr"/>
+      <c r="G124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>tab_permissions</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>tables_metadata</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr"/>
+      <c r="E126" s="3" t="inlineStr"/>
+      <c r="F126" s="3" t="inlineStr"/>
+      <c r="G126" s="3" t="inlineStr"/>
+      <c r="H126" s="3" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>tabs</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>target_item</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>target_logic</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>target_plan</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>telephony_config</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>telephony_user</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr"/>
+      <c r="F134" s="7" t="inlineStr"/>
+      <c r="G134" s="7" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr"/>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr"/>
+      <c r="E136" s="3" t="inlineStr"/>
+      <c r="F136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="inlineStr"/>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr"/>
+      <c r="E137" s="3" t="inlineStr"/>
+      <c r="F137" s="3" t="inlineStr"/>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>user_gmail_tokens</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr"/>
+      <c r="F138" s="7" t="inlineStr"/>
+      <c r="G138" s="7" t="inlineStr"/>
+      <c r="H138" s="7" t="inlineStr"/>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>user_group</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>user_group_profiles</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="7" t="inlineStr"/>
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr"/>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>user_group_public_groups</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr"/>
+      <c r="F141" s="7" t="inlineStr"/>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr"/>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>user_group_users</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
+      <c r="G142" s="4" t="inlineStr"/>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>user_login_history</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>user_outlook_tokens</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr"/>
+      <c r="G144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr"/>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>users_user_permissions</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr"/>
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="inlineStr"/>
+      <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>visit</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>webhook</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>workflow</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>workflow_edge</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>workflow_node</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>workflow_rules</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr"/>
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
         </is>
       </c>
     </row>

--- a/objects_audit.xlsx
+++ b/objects_audit.xlsx
@@ -214,8 +214,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllObjects" displayName="AllObjects" ref="A1:Q109" headerRowCount="1">
-  <autoFilter ref="A1:Q109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllObjects" displayName="AllObjects" ref="A1:Q108" headerRowCount="1">
+  <autoFilter ref="A1:Q108"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Category"/>
     <tableColumn id="2" name="Subcategory"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MigrationPlan" displayName="MigrationPlan" ref="A1:G88" headerRowCount="1">
-  <autoFilter ref="A1:G88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MigrationPlan" displayName="MigrationPlan" ref="A1:G87" headerRowCount="1">
+  <autoFilter ref="A1:G87"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Wave"/>
@@ -270,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DDLCrossCheck" displayName="DDLCrossCheck" ref="A1:I110" headerRowCount="1">
-  <autoFilter ref="A1:I110"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DDLCrossCheck" displayName="DDLCrossCheck" ref="A1:I109" headerRowCount="1">
+  <autoFilter ref="A1:I109"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Table Name"/>
     <tableColumn id="2" name="In Registry"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6640,17 +6640,17 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>dashboard_folder</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Folder</t>
+          <t>Email Record</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Folders</t>
+          <t>Email Records</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -6666,7 +6666,7 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>Deployed</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -6681,19 +6681,15 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="inlineStr">
-        <is>
-          <t>DaF</t>
-        </is>
-      </c>
+      <c r="N81" s="3" t="n"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -6719,17 +6715,17 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Email Record</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Email Records</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -6745,7 +6741,7 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -6760,15 +6756,19 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="n"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>EvX</t>
+        </is>
+      </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -6794,17 +6794,17 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>incentive_slab</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Incentive Slab</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Incentive Slabs</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>EvX</t>
+          <t>InS</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>incentive_slab</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Incentive Slab</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Incentive Slabs</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -6899,7 +6899,7 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>Deployed</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -6914,19 +6914,15 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
-        <is>
-          <t>InS</t>
-        </is>
-      </c>
+      <c r="N84" s="3" t="n"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -6952,17 +6948,17 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>invoice_item</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Invoice Item</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Invoice Items</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -7027,17 +7023,17 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>invoice_item</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Invoice Item</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Invoice Items</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -7050,7 +7046,11 @@
           <t>False</t>
         </is>
       </c>
-      <c r="H86" s="3" t="n"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
           <t>Deployed</t>
@@ -7102,17 +7102,17 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>leads</t>
+          <t>opportunity</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Opportunity</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Opportunities</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -7125,11 +7125,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
+      <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
           <t>Deployed</t>
@@ -7181,17 +7177,17 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>opportunity</t>
+          <t>opportunity_lineitem</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Opportunity</t>
+          <t>Opportunity Line Item</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Opportunities</t>
+          <t>Opportunity Line Items</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -7256,17 +7252,17 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>opportunity_lineitem</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Opportunity Line Item</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Opportunity Line Items</t>
+          <t>Periods</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -7282,7 +7278,7 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -7297,15 +7293,19 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="n"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>PeX</t>
+        </is>
+      </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Periods</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -7357,7 +7357,7 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>Deployed</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -7372,19 +7372,15 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N90" s="3" t="inlineStr">
-        <is>
-          <t>PeX</t>
-        </is>
-      </c>
+      <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7410,17 +7406,17 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product_category</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Category</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>Product Categories</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -7485,17 +7481,17 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>product_category</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Product Category</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Product Categories</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -7560,17 +7556,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>quote_line_item</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Quote Line Item</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Quote Line Items</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -7635,17 +7631,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>quote_line_item</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Quote Line Item</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Quote Line Items</t>
+          <t>Targets</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -7710,17 +7706,17 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>target_item</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target Item</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Targets</t>
+          <t>Target Items</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -7736,7 +7732,7 @@
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -7751,15 +7747,19 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="n"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>TaI</t>
+        </is>
+      </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7785,17 +7785,17 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>target_item</t>
+          <t>target_logic</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Target Item</t>
+          <t>Target Logic</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Target Items</t>
+          <t>Target Logics</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -7811,7 +7811,7 @@
       <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>Deployed</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -7826,19 +7826,15 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
-          <t>TaI</t>
-        </is>
-      </c>
+      <c r="N96" s="3" t="n"/>
       <c r="O96" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7864,17 +7860,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>target_logic</t>
+          <t>target_plan</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Target Logic</t>
+          <t>Target Plan</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Target Logics</t>
+          <t>Target Plans</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -7890,7 +7886,7 @@
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -7905,15 +7901,19 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="n"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>TaP</t>
+        </is>
+      </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7927,79 +7927,79 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>BUSINESS / STANDARD</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Standard business object</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>target_plan</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Target Plan</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>Target Plans</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>BUSINESS / CUSTOM</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>User-defined</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>an_object_for_testing</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>AN object for Testing</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>AN object for Testings</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K98" s="3" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>TaP</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>AnOft</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P98" s="3" t="inlineStr"/>
-      <c r="Q98" s="3" t="inlineStr">
+      <c r="P98" s="4" t="inlineStr"/>
+      <c r="Q98" s="4" t="inlineStr">
         <is>
           <t>Keep raw SQL — dynamic schema via metadata gateway</t>
         </is>
@@ -8018,17 +8018,17 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>an_object_for_testing</t>
+          <t>business</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>AN object for Testing</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>AN object for Testings</t>
+          <t>Businesss</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -8044,32 +8044,32 @@
       <c r="H99" s="4" t="n"/>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>In Development</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>AnOft</t>
+          <t>BuX</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -8097,17 +8097,17 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Businesss</t>
+          <t>Calls</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -8123,32 +8123,32 @@
       <c r="H100" s="4" t="n"/>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>In Development</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>BuX</t>
+          <t>CaX</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Calls</t>
+          <t>Collections</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -8202,32 +8202,32 @@
       <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>In Development</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>CaX</t>
+          <t>CoX</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8255,17 +8255,17 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>CoX</t>
+          <t>CuX</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -8334,17 +8334,17 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -8360,7 +8360,7 @@
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>In Development</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -8370,22 +8370,22 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>CuX</t>
+          <t>IsX</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -8413,17 +8413,17 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>leave</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Leaves</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -8439,32 +8439,32 @@
       <c r="H104" s="4" t="n"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>In Development</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>IsX</t>
+          <t>LeX</t>
         </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8492,17 +8492,17 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>leave</t>
+          <t>location_track</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Location Track</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Leaves</t>
+          <t>Location Tracks</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>LeX</t>
+          <t>LoT</t>
         </is>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>location_track</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Location Track</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Location Tracks</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -8597,22 +8597,22 @@
       <c r="H106" s="4" t="n"/>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>In Development</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>LoT</t>
+          <t>TeX</t>
         </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8650,17 +8650,17 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>ticket</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Ticket</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Tickets</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -8676,7 +8676,7 @@
       <c r="H107" s="4" t="n"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>In Development</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>TeX</t>
+          <t>TiX</t>
         </is>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>ticket</t>
+          <t>visit</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Ticket</t>
+          <t>Visit</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Tickets</t>
+          <t>Visits</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -8760,27 +8760,27 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>TiX</t>
+          <t>ViX</t>
         </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8790,85 +8790,6 @@
       </c>
       <c r="P108" s="4" t="inlineStr"/>
       <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>Keep raw SQL — dynamic schema via metadata gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>BUSINESS / CUSTOM</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>User-defined</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>visit</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Visits</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>custom</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>In Development</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M109" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>ViX</t>
-        </is>
-      </c>
-      <c r="O109" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="inlineStr"/>
-      <c r="Q109" s="4" t="inlineStr">
         <is>
           <t>Keep raw SQL — dynamic schema via metadata gateway</t>
         </is>
@@ -8888,7 +8809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11121,12 +11042,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>dashboard_folder</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Dashboard Folder</t>
+          <t>Email Record</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -11158,12 +11079,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Email Record</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -11195,12 +11116,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>incentive_slab</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Incentive Slab</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -11232,12 +11153,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>incentive_slab</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Incentive Slab</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -11269,12 +11190,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>invoice_item</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Invoice Item</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -11301,22 +11222,22 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>invoice_item</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Invoice Item</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Standard business object</t>
+          <t>User-defined</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -11338,22 +11259,22 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>User-defined</t>
+          <t>Standard business object</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -11375,22 +11296,22 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>leads</t>
+          <t>leave</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Standard business object</t>
+          <t>User-defined</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -11417,12 +11338,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>leave</t>
+          <t>location_track</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Location Track</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -11449,22 +11370,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>location_track</t>
+          <t>opportunity</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Location Track</t>
+          <t>Opportunity</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>User-defined</t>
+          <t>Standard business object</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -11491,12 +11412,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>opportunity</t>
+          <t>opportunity_lineitem</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Opportunity</t>
+          <t>Opportunity Line Item</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -11528,12 +11449,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>opportunity_lineitem</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Opportunity Line Item</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -11565,12 +11486,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -11602,12 +11523,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product_category</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Category</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -11639,12 +11560,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>product_category</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Product Category</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -11676,12 +11597,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>quote_line_item</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Quote Line Item</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -11713,12 +11634,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>quote_line_item</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Quote Line Item</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -11750,12 +11671,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>target_item</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target Item</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -11787,12 +11708,12 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>target_item</t>
+          <t>target_logic</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Target Item</t>
+          <t>Target Logic</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -11824,12 +11745,12 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>target_logic</t>
+          <t>target_plan</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Target Logic</t>
+          <t>Target Plan</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -11856,22 +11777,22 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>target_plan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Target Plan</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Standard business object</t>
+          <t>User-defined</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -11898,12 +11819,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>ticket</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Ticket</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -11935,12 +11856,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>ticket</t>
+          <t>visit</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Ticket</t>
+          <t>Visit</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -11954,43 +11875,6 @@
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Dynamic schema — cannot be a static Django model</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Phase 5 — Business objects (raw SQL via gateway)</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>visit</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>User-defined</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Route through hardened ORM gateway (sql.Identifier + schema authority)</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Dynamic schema — cannot be a static Django model</t>
         </is>
@@ -13141,7 +13025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -13811,36 +13695,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>dashboard_folder</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>VESTIGIAL — registered but no DDL anywhere</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>dashboard_folder_sharing</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>dashboard_folder_sharing</t>
+          <t>dashboard_folders</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -13869,40 +13757,36 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>dashboard_folders</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>django_admin_log</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>OK — Django/Celery framework table</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>django_admin_log</t>
+          <t>django_celery_beat_clockedschedule</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -13929,7 +13813,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_clockedschedule</t>
+          <t>django_celery_beat_crontabschedule</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -13956,7 +13840,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_crontabschedule</t>
+          <t>django_celery_beat_intervalschedule</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -13983,7 +13867,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_intervalschedule</t>
+          <t>django_celery_beat_periodictask</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -14010,7 +13894,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_periodictask</t>
+          <t>django_celery_beat_periodictasks</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -14037,7 +13921,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_periodictasks</t>
+          <t>django_celery_beat_solarschedule</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -14064,7 +13948,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>django_celery_beat_solarschedule</t>
+          <t>django_content_type</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -14091,7 +13975,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>django_content_type</t>
+          <t>django_migrations</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -14118,7 +14002,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>django_migrations</t>
+          <t>django_session</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -14143,36 +14027,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>django_session</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>OK — Django/Celery framework table</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_provider_setup</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -14182,15 +14070,15 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -14203,7 +14091,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>email_provider_setup</t>
+          <t>email_templates</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -14234,7 +14122,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>email_templates</t>
+          <t>event</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -14244,15 +14132,15 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
@@ -14265,7 +14153,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>facebook_lead</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -14275,17 +14163,17 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -14294,71 +14182,71 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>facebook_lead</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>facebookleadwebhooks</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>GAP — DDL exists, registry row missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>field_history_log</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>facebookleadwebhooks</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>GAP — DDL exists, registry row missing</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>field_history_log</t>
+          <t>field_mapping</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -14389,7 +14277,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>field_mapping</t>
+          <t>field_permissions</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -14410,7 +14298,11 @@
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14420,7 +14312,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>field_permissions</t>
+          <t>field_tracking_config</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -14441,11 +14333,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14455,7 +14343,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>field_tracking_config</t>
+          <t>fields</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -14476,7 +14364,11 @@
       <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14486,7 +14378,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>fields</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -14499,19 +14391,15 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14521,7 +14409,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>homepage_assignment</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -14534,12 +14422,12 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr"/>
@@ -14552,7 +14440,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>homepage_assignment</t>
+          <t>incentive_slab</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -14562,15 +14450,15 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
@@ -14583,7 +14471,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>incentive_slab</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -14614,7 +14502,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>invoice_item</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -14643,67 +14531,67 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>invoice_item</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>issue</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>OK — custom (dynamic DDL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>landing_numbers</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>issue</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>custom</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>OK — custom (dynamic DDL)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>landing_numbers</t>
+          <t>layout_assignment</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -14732,125 +14620,125 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>layout_assignment</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>lead_capture</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>VESTIGIAL — registered but no DDL anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>lead_capture</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>OK — custom (dynamic DDL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>listviews</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>VESTIGIAL — registered but no DDL anywhere</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>leave</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>custom</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>OK — custom (dynamic DDL)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>listviews</t>
+          <t>location_track</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -14860,15 +14748,15 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr"/>
@@ -14881,7 +14769,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>location_track</t>
+          <t>message</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -14891,17 +14779,17 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -14912,7 +14800,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -14925,14 +14813,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -14943,7 +14831,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>object</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -14964,7 +14852,11 @@
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14974,7 +14866,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>object_permissions</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -15009,7 +14901,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>object_permissions</t>
+          <t>opportunity</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -15019,22 +14911,18 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr"/>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15044,7 +14932,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>opportunity</t>
+          <t>opportunity_lineitem</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -15075,7 +14963,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>opportunity_lineitem</t>
+          <t>org_company</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -15085,15 +14973,15 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr"/>
@@ -15106,7 +14994,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>org_company</t>
+          <t>organizations</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -15119,14 +15007,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H65" s="4" t="inlineStr"/>
       <c r="I65" s="4" t="inlineStr">
         <is>
@@ -15137,7 +15025,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>organizations</t>
+          <t>page_builder</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -15150,14 +15038,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -15168,7 +15056,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>page_builder</t>
+          <t>page_builder_assignment</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -15199,7 +15087,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>page_builder_assignment</t>
+          <t>page_component</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -15230,7 +15118,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>page_component</t>
+          <t>page_layouts</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -15261,7 +15149,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>page_layouts</t>
+          <t>path_builder</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -15292,7 +15180,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>path_builder</t>
+          <t>period</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -15302,15 +15190,15 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr"/>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr"/>
@@ -15323,7 +15211,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -15354,7 +15242,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product_category</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -15385,7 +15273,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>product_category</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -15395,18 +15283,22 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15416,7 +15308,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -15426,22 +15318,18 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H75" s="4" t="inlineStr"/>
       <c r="I75" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15451,7 +15339,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>quote_line_item</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -15482,7 +15370,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>quote_line_item</t>
+          <t>report</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -15492,15 +15380,15 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr"/>
@@ -15513,7 +15401,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>report_folder</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -15544,7 +15432,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>report_folder</t>
+          <t>report_folder_sharing</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -15575,7 +15463,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>report_folder_sharing</t>
+          <t>salesforce_metadata</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -15588,14 +15476,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D80" s="4" t="inlineStr"/>
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
@@ -15606,7 +15494,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>salesforce_metadata</t>
+          <t>salesforce_settings</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -15637,7 +15525,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>salesforce_settings</t>
+          <t>salesforce_sync</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -15668,7 +15556,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>salesforce_sync</t>
+          <t>search_layouts</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -15681,14 +15569,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E83" s="4" t="inlineStr"/>
       <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr">
         <is>
@@ -15699,7 +15587,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>search_layouts</t>
+          <t>session_log</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -15712,14 +15600,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D84" s="4" t="inlineStr"/>
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr">
         <is>
@@ -15730,7 +15618,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>session_log</t>
+          <t>shared_records</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -15743,14 +15631,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr"/>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr"/>
       <c r="I85" s="4" t="inlineStr">
         <is>
@@ -15761,7 +15649,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>shared_records</t>
+          <t>sharing_records</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -15782,7 +15670,11 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15792,7 +15684,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>sharing_records</t>
+          <t>tab_permissions</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -15827,7 +15719,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>tab_permissions</t>
+          <t>target</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -15837,22 +15729,18 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15862,7 +15750,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>target_item</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -15893,7 +15781,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>target_item</t>
+          <t>target_logic</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -15924,7 +15812,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>target_logic</t>
+          <t>target_plan</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -15955,7 +15843,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>target_plan</t>
+          <t>task</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -15965,15 +15853,15 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr"/>
@@ -15986,7 +15874,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>telephony_config</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -16017,7 +15905,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>telephony_config</t>
+          <t>telephony_user</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -16046,40 +15934,36 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>telephony_user</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>OK — custom (dynamic DDL)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>ticket</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -16104,36 +15988,40 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>ticket</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>custom</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>OK — custom (dynamic DDL)</t>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>user_gmail_tokens</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>user_gmail_tokens</t>
+          <t>user_group</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -16154,7 +16042,11 @@
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="inlineStr"/>
-      <c r="H98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16164,7 +16056,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>user_group</t>
+          <t>user_group_profiles</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -16185,11 +16077,7 @@
       <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16199,7 +16087,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>user_group_profiles</t>
+          <t>user_group_public_groups</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -16230,7 +16118,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>user_group_public_groups</t>
+          <t>user_group_users</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -16251,7 +16139,11 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16261,7 +16153,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>user_group_users</t>
+          <t>user_login_history</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -16274,19 +16166,15 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr"/>
       <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16296,7 +16184,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>user_login_history</t>
+          <t>user_outlook_tokens</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -16309,14 +16197,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="inlineStr"/>
       <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
@@ -16327,7 +16215,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>user_outlook_tokens</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -16340,14 +16228,18 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
@@ -16358,7 +16250,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>visit</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -16368,21 +16260,17 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
@@ -16393,7 +16281,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>visit</t>
+          <t>webhook</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -16403,17 +16291,17 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="H106" s="4" t="inlineStr"/>
       <c r="I106" s="4" t="inlineStr">
         <is>
@@ -16424,7 +16312,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>webhook</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -16437,14 +16325,14 @@
           <t>setup</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
@@ -16455,7 +16343,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>workflow_edge</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -16486,7 +16374,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>workflow_edge</t>
+          <t>workflow_node</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -16509,37 +16397,6 @@
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>workflow_node</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr"/>
-      <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
